--- a/ADC_prevodniky.xlsx
+++ b/ADC_prevodniky.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\panto\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9F088E-F788-4248-A503-F7F83F49A53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB08A44-1CE2-4B69-AC1A-B5E52CBC23BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5197164-3AB9-4333-A436-38823C333596}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
   <si>
     <t>ADC převodníky</t>
   </si>
@@ -150,6 +150,120 @@
   </si>
   <si>
     <t>bipolar power supply</t>
+  </si>
+  <si>
+    <t>Interní sample and hold</t>
+  </si>
+  <si>
+    <t>https://www.analog.com/media/en/technical-documentation/data-sheets/ad7177-2.pdf</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
+    <t>Komunikace s čipem(možná)</t>
+  </si>
+  <si>
+    <t>https://www.alldatasheet.com/datasheet-pdf/view/155397/TI/ADC0808.html</t>
+  </si>
+  <si>
+    <t>8080bus</t>
+  </si>
+  <si>
+    <t>https://www.analog.com/media/en/technical-documentation/data-sheets/ad7124-4.pdf</t>
+  </si>
+  <si>
+    <t>Operační zesilovač</t>
+  </si>
+  <si>
+    <t>TL081</t>
+  </si>
+  <si>
+    <t>GBW(Gain-bandwidth product)</t>
+  </si>
+  <si>
+    <t>5.25MHz</t>
+  </si>
+  <si>
+    <t>OPAx350</t>
+  </si>
+  <si>
+    <t>38MHz</t>
+  </si>
+  <si>
+    <t>OPAx354</t>
+  </si>
+  <si>
+    <t>250MHz</t>
+  </si>
+  <si>
+    <t>Slew Rate[V/µs]</t>
+  </si>
+  <si>
+    <t>LMH6642</t>
+  </si>
+  <si>
+    <t>Komparační zesilovač</t>
+  </si>
+  <si>
+    <t>130MHz</t>
+  </si>
+  <si>
+    <t>Zpoždění</t>
+  </si>
+  <si>
+    <t>Odkaz na datasheet</t>
+  </si>
+  <si>
+    <t>https://www.analog.com/media/en/technical-documentation/data-sheets/2440fe.pdf</t>
+  </si>
+  <si>
+    <t>BA82901YF-CE2</t>
+  </si>
+  <si>
+    <t>1.3 µs</t>
+  </si>
+  <si>
+    <t>https://ww1.microchip.com/downloads/en/devicedoc/21290f.pdf</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/ads1015.pdf</t>
+  </si>
+  <si>
+    <t>I 2C</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/ads8860.pdf?ts=1792853385933&amp;ref_url=https%253A%252F%252Fwww.ti.com%252F</t>
+  </si>
+  <si>
+    <t>https://www.analog.com/media/en/technical-documentation/data-sheets/ad7685.pdf</t>
+  </si>
+  <si>
+    <t>https://www.analog.com/media/en/technical-documentation/data-sheets/AD4003-4007-4011.pdf</t>
+  </si>
+  <si>
+    <t>https://www.analog.com/media/en/technical-documentation/data-sheets/ad4060.pdf</t>
+  </si>
+  <si>
+    <t>I3C</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/adc0820-n.pdf</t>
+  </si>
+  <si>
+    <t>Tri-state data output(8pins)</t>
+  </si>
+  <si>
+    <t>https://www.analog.com/media/en/technical-documentation/data-sheets/ad7705_7706.pdf</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/lit/ds/symlink/ads1148-q1.pdf?ts=1792853329410&amp;ref_url=https%253A%252F%252Fwww.ti.com%252F</t>
+  </si>
+  <si>
+    <t>AD8065</t>
+  </si>
+  <si>
+    <t>145Mhz</t>
   </si>
 </sst>
 </file>
@@ -160,7 +274,7 @@
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;Kč&quot;;[Red]\-#,##0\ &quot;Kč&quot;"/>
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;Kč&quot;;[Red]\-#,##0.00\ &quot;Kč&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,8 +332,20 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF161616"/>
+      <name val="Inherit"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,8 +364,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -348,11 +480,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -409,6 +578,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="6" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -745,19 +941,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15694E16-BC2E-47A7-B28F-D313EFD4BD3B}">
-  <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="21" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
     <col min="4" max="5" width="17.28515625" customWidth="1"/>
     <col min="6" max="6" width="42.28515625" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="36.85546875" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" customWidth="1"/>
-    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.140625" customWidth="1"/>
+    <col min="12" max="12" width="61.28515625" customWidth="1"/>
+    <col min="13" max="13" width="31" customWidth="1"/>
+    <col min="14" max="14" width="25.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="16" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -771,8 +974,11 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" ht="16.5" thickBot="1">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>0</v>
@@ -795,17 +1001,26 @@
       <c r="H2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75">
       <c r="A3" s="2"/>
       <c r="B3" s="15" t="s">
         <v>2</v>
@@ -828,15 +1043,24 @@
       <c r="H3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="19">
         <v>947</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L3" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="17"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="2"/>
       <c r="B4" s="1" t="s">
         <v>8</v>
@@ -859,15 +1083,24 @@
       <c r="H4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="9">
         <v>201</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="L4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="9"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" ht="17.25">
       <c r="A5" s="2"/>
       <c r="B5" s="14" t="s">
         <v>9</v>
@@ -890,15 +1123,24 @@
       <c r="H5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="13">
         <v>370</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L5" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="13"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="2"/>
       <c r="B6" s="12" t="s">
         <v>12</v>
@@ -921,15 +1163,24 @@
       <c r="H6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="13">
         <v>490</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" ht="16.5">
       <c r="A7" s="2"/>
       <c r="B7" s="7" t="s">
         <v>15</v>
@@ -952,15 +1203,24 @@
       <c r="H7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="9">
         <v>32</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="L7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="9"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" ht="16.5">
       <c r="A8" s="2"/>
       <c r="B8" s="7" t="s">
         <v>16</v>
@@ -983,17 +1243,26 @@
       <c r="H8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="9">
         <v>83</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="L8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" ht="16.5">
       <c r="A9" s="2"/>
       <c r="B9" s="7" t="s">
         <v>17</v>
@@ -1016,17 +1285,26 @@
       <c r="H9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" s="9">
         <v>109</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="L9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5">
       <c r="A10" s="2"/>
       <c r="B10" s="7" t="s">
         <v>19</v>
@@ -1049,15 +1327,24 @@
       <c r="H10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="10">
         <v>462</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="L10" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" ht="16.5">
       <c r="A11" s="2"/>
       <c r="B11" s="11" t="s">
         <v>20</v>
@@ -1080,15 +1367,24 @@
       <c r="H11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="13">
         <v>678</v>
       </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="L11" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5">
       <c r="A12" s="2"/>
       <c r="B12" s="7" t="s">
         <v>21</v>
@@ -1111,15 +1407,24 @@
       <c r="H12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="9">
         <v>867</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="L12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="9"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" ht="16.5">
       <c r="A13" s="2"/>
       <c r="B13" s="7" t="s">
         <v>22</v>
@@ -1142,46 +1447,64 @@
       <c r="H13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="2"/>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="26">
         <v>8</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="26">
         <v>2</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="12" t="s">
+      <c r="G14" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="27">
         <v>201</v>
       </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L14" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="27"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="2"/>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -1204,15 +1527,24 @@
       <c r="H15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="9">
         <v>385</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="L15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" ht="16.5">
       <c r="A16" s="2"/>
       <c r="B16" s="7" t="s">
         <v>34</v>
@@ -1235,15 +1567,24 @@
       <c r="H16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="9">
         <v>249</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="1"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="2"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1254,11 +1595,14 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="2"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1269,11 +1613,14 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="2"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1284,11 +1631,14 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1302,8 +1652,11 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1317,71 +1670,124 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>52</v>
+      </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="F22" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>56</v>
+      </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="B23" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="12">
+        <v>20</v>
+      </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="F23" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>60</v>
+      </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="12">
+        <v>22</v>
+      </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="B25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="1">
+        <v>150</v>
+      </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="B26" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="26">
+        <v>130</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1390,11 +1796,20 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" ht="16.5">
+      <c r="B27" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="12">
+        <v>180</v>
+      </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -1403,11 +1818,14 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1416,11 +1834,14 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -1429,11 +1850,14 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1442,11 +1866,14 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -1455,11 +1882,14 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1468,8 +1898,12 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ADC_prevodniky.xlsx
+++ b/ADC_prevodniky.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\panto\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB08A44-1CE2-4B69-AC1A-B5E52CBC23BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27E5273-C209-40EC-A681-2AC08294D619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5197164-3AB9-4333-A436-38823C333596}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="84">
   <si>
     <t>ADC převodníky</t>
   </si>
@@ -264,6 +264,33 @@
   </si>
   <si>
     <t>145Mhz</t>
+  </si>
+  <si>
+    <t>Integrovaný Mos spínač</t>
+  </si>
+  <si>
+    <t>CD4066B</t>
+  </si>
+  <si>
+    <t>file:///C:/Users/panto/Downloads/cd4066b.pdf</t>
+  </si>
+  <si>
+    <t>74HC4066D</t>
+  </si>
+  <si>
+    <t>https://octopart.com/datasheet/toshiba/74HC4066D</t>
+  </si>
+  <si>
+    <t>TS5A3159</t>
+  </si>
+  <si>
+    <t>NC7SB3157P6X</t>
+  </si>
+  <si>
+    <t>https://octopart.com/datasheet/onsemi/NC7SB3157P6X</t>
+  </si>
+  <si>
+    <t>Počet  nezávislých kanálů</t>
   </si>
 </sst>
 </file>
@@ -274,7 +301,7 @@
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;Kč&quot;;[Red]\-#,##0\ &quot;Kč&quot;"/>
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;Kč&quot;;[Red]\-#,##0.00\ &quot;Kč&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,6 +371,15 @@
       <color rgb="FF161616"/>
       <name val="Inherit"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -518,10 +554,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -607,8 +644,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hypertextový odkaz" xfId="1" builtinId="8"/>
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -941,12 +989,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15694E16-BC2E-47A7-B28F-D313EFD4BD3B}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
     <col min="3" max="3" width="27.85546875" customWidth="1"/>
-    <col min="4" max="5" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="37" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
     <col min="6" max="6" width="42.28515625" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="36.85546875" customWidth="1"/>
@@ -1855,11 +1904,17 @@
       <c r="O29" s="2"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="B30" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="22"/>
+      <c r="F30" s="31"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -1871,10 +1926,18 @@
       <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="2"/>
+      <c r="B31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="12">
+        <v>4</v>
+      </c>
+      <c r="D31" s="9">
+        <v>21</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -1887,10 +1950,18 @@
       <c r="O31" s="2"/>
     </row>
     <row r="32" spans="1:16">
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="2"/>
+      <c r="B32" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="12">
+        <v>4</v>
+      </c>
+      <c r="D32" s="9">
+        <v>11</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -1902,6 +1973,40 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9">
+        <v>11</v>
+      </c>
+      <c r="E33" s="30"/>
+      <c r="F33" s="32"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="9">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
